--- a/ديمو/templates/05_العقد_والمقايسة.xlsx
+++ b/ديمو/templates/05_العقد_والمقايسة.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -754,88 +754,306 @@
       <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>تأمين ضمان الأعمال %</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>نسبة الصرف مع المستخلص الشهري % *</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>retention_pct</t>
+          <t>pay_monthly_pct</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>بيتخصم من كل مستخلص ويتفرج عنه بعد الضمان</t>
+          <t>232: 70% — 231: 90%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>خصم ضريبي من المنبع %</t>
+          <t>نسبة محجوزة لحد تسليم خرائط As-Built %</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>tax_pct</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
+          <t>pay_asbuilt_pct</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>232: 20% — 231: 0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>دمغة %</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr"/>
+          <t>نسبة محجوزة لحد التسليم الابتدائي %</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>stamp_pct</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
+          <t>pay_handover_pct</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>232 و 231: 10%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>الدفعة المقدمة %</t>
+          <t>نسبة صرف أعمال التخطيط %</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>advance_pct</t>
+          <t>planning_pay_pct</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>لو فيه دفعة مقدمة بتسترد من المستخلصات</t>
+          <t>التخطيط بيتصرف 100% بعد الانتهاء منه</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>قيمة العقد</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr"/>
+          <t>خطاب الضمان النهائي % من قيمة أمر التكليف</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>final_guarantee_pct</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>بيتقدم مع كل أمر تكليف</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>غرامة التأخير % لكل أسبوع</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>delay_fine_pct_week</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>231: 2% أسبوعياً</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>الحد الأقصى للغرامة %</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>delay_fine_cap_pct</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>من قيمة الأعمال المتأخرة</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>مدة الضمان الفني (شهور)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>warranty_months</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>علاوة خارج النطاق</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>5% / 10% / 15% سيناء</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>out_of_scope_uplift</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>حتى 25% (أو حسب ملحق البرقية)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>دمغة المهن الهندسية % (على أمر التكليف)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>stamp_engineering_pct</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>بتتدفع مرة واحدة مع أمر التكليف</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>دمغة مصممي الفنون التطبيقية %</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>stamp_applied_arts_pct</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>دمغة التشييد والبناء %</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>stamp_construction_pct</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>خصم ضريبي من المنبع %</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>tax_pct</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>من المالية</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>تأمين ضمان أعمال إضافي % (لو موجود)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>retention_pct</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>العقود الحالية مفيهاش — الضمان بخطاب ضمان نهائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>الدفعة المقدمة % (لو موجودة)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>advance_pct</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>العقود الحالية مفيهاش دفعة مقدمة</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>قيمة العقد (بعد آخر ملحق)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
           <t>contract_value</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>لو فاضي بتتحسب من المقايسة</t>
         </is>

--- a/ديمو/templates/05_العقد_والمقايسة.xlsx
+++ b/ديمو/templates/05_العقد_والمقايسة.xlsx
@@ -264,31 +264,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>المنظومة</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>بالتدرج: 1-1-1-1 — صفوف العناوين من غير وحدة</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>فاضي = صف عنوان (مجموعة)</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>فاضي أو صفر = البند مالوش سعر في العقد (أي فوترة عليه تبقى فئة C5)</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1274,7 +1249,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1284,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1391,6 +1365,37 @@
       <c r="A16" s="17" t="inlineStr">
         <is>
           <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>شرح الأعمدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>• [المقايسة] رقم البند: بالتدرج: 1-1-1-1 — صفوف العناوين من غير وحدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>• [المقايسة] الوحدة: فاضي = صف عنوان (مجموعة)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>• [المقايسة] سعر الوحدة: فاضي أو صفر = البند مالوش سعر في العقد (أي فوترة عليه تبقى فئة C5)</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1432,6 +1437,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"المقايسة": [["1", "الإعمال المدنيــة", "", "", "", ""], ["1-1", "غرف التفتيش", "", "", "", ""], ["1-1-1-2", "غرفة تفتيش طراز HH-I", "عدد", "180", "26000", "أعمال مدنية"], ["1-9-1", "حفر ضيق Micro trenching عرض 10 إلى 13 سم", "م.ط", "50000", "0", "أعمال مدنية"], ["2-4-7", "pulling of HDPE Single Microduct", "م.ط", "80000", "0", "تركيبات"]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ديمو/templates/05_العقد_والمقايسة.xlsx
+++ b/ديمو/templates/05_العقد_والمقايسة.xlsx
@@ -604,14 +604,14 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>زي ما هو مكتوب في برقية القبول</t>
+          <t>كما ورد في برقية القبول</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>كود الشركة *</t>
+          <t>كود الشركة المنفذة *</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>من قالب الشركات</t>
+          <t>من نموذج الشركات المنفذة</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>نسبة الصرف مع المستخلص الشهري % *</t>
+          <t>نسبة السداد مع المستخلص الشهري % *</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -751,7 +751,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>نسبة محجوزة لحد تسليم خرائط As-Built %</t>
+          <t>نسبة محتجزة لحين تسليم خرائط ما بعد التنفيذ (As-Built) %</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -771,7 +771,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>نسبة محجوزة لحد التسليم الابتدائي %</t>
+          <t>نسبة محتجزة لحين الاستلام الابتدائي %</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -791,7 +791,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>نسبة صرف أعمال التخطيط %</t>
+          <t>نسبة سداد أعمال التخطيط %</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>التخطيط بيتصرف 100% بعد الانتهاء منه</t>
+          <t>تُسدَّد أعمال التخطيط بنسبة 100% بعد الانتهاء منها</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>بيتقدم مع كل أمر تكليف</t>
+          <t>يُقدَّم مع كل أمر تكليف</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>بتتدفع مرة واحدة مع أمر التكليف</t>
+          <t>تُسدَّد مرة واحدة مع أمر التكليف</t>
         </is>
       </c>
     </row>
@@ -972,14 +972,14 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>من المالية</t>
+          <t>تحدده الإدارة المالية</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>تأمين ضمان أعمال إضافي % (لو موجود)</t>
+          <t>تأمين ضمان أعمال إضافي % (إن وُجد)</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -992,14 +992,14 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>العقود الحالية مفيهاش — الضمان بخطاب ضمان نهائي</t>
+          <t>لا تتضمنه العقود الحالية — الضمان بخطاب الضمان النهائي</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>الدفعة المقدمة % (لو موجودة)</t>
+          <t>الدفعة المقدمة % (إن وُجدت)</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>العقود الحالية مفيهاش دفعة مقدمة</t>
+          <t>لا تتضمن العقود الحالية دفعة مقدمة</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>لو فاضي بتتحسب من المقايسة</t>
+          <t>إذا تُركت فارغة تُحتسب من جدول الكميات والأسعار</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>كمية العقد</t>
+          <t>الكمية التعاقدية</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
@@ -1238,13 +1238,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="E3:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="قيمة غير مسموحة" error="اختار من القائمة" type="list">
+    <dataValidation sqref="F3:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="قيمة غير مسموحة" error="يرجى الاختيار من القائمة" type="list">
       <formula1>"أعمال مدنية,تركيبات,كهربية,توريد,توريد وتركيب,تخطيط ورسومات,خدمات,صيانة"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1267,21 +1267,21 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>قالب العقد والمقايسة</t>
+          <t>نموذج العقد وجدول الكميات والأسعار</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>الغرض: تعريف العقد وبنوده وأسعاره — الأسعار دي اللي السيستم بيحسب بيها كل المستخلصات.</t>
+          <t>الغرض: تعريف العقد وبنوده وأسعاره — وهي الأسعار التي تحتسب بها المنظومة جميع المستخلصات.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>مين بيرفعه: الشئون الفنية.</t>
+          <t>الجهة المسؤولة عن الرفع: الشئون الفنية.</t>
         </is>
       </c>
     </row>
@@ -1291,28 +1291,28 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>• رقم البند بالشرطة (1-1-1-1) أو النقطة (1.1.1.1) — السيستم بيوحدهم.</t>
+          <t>• يُكتب رقم البند بالشرطة (1-1-1-1) أو بالنقطة (1.1.1.1) — وتوحّد المنظومة الصيغتين.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>• الصف اللي من غير وحدة بيتعامل كعنوان مجموعة، ومش بيتفوتر عليه.</t>
+          <t>• يُعامَل الصف الذي لا يتضمن وحدة كعنوان مجموعة، ولا تجوز الفوترة عليه.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>• ممكن تنسخ المقايسة المعتمدة زي ما هي في شيت المقايسة (نفس ترتيب الأعمدة: مسلسل، البيان، الوحدة، الكمية، سعر الوحدة).</t>
+          <t>• يمكن نسخ المقايسة المعتمدة كما هي في ورقة عمل المقايسة (بترتيب الأعمدة نفسه: مسلسل، البيان، الوحدة، الكمية، سعر الوحدة).</t>
         </is>
       </c>
     </row>
@@ -1322,49 +1322,49 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>
@@ -1374,28 +1374,28 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>شرح الأعمدة</t>
+          <t>إيضاح الأعمدة</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>• [المقايسة] رقم البند: بالتدرج: 1-1-1-1 — صفوف العناوين من غير وحدة</t>
+          <t>• [المقايسة] رقم البند: بالتدرج: 1-1-1-1 — صفوف العناوين بدون وحدة</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>• [المقايسة] الوحدة: فاضي = صف عنوان (مجموعة)</t>
+          <t>• [المقايسة] الوحدة: فارغ = صف عنوان (مجموعة)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>• [المقايسة] سعر الوحدة: فاضي أو صفر = البند مالوش سعر في العقد (أي فوترة عليه تبقى فئة C5)</t>
+          <t>• [المقايسة] سعر الوحدة: فارغ أو صفر = البند غير مُسعّر في العقد (أي فوترة عليه تُصنَّف ضمن الفئة C5)</t>
         </is>
       </c>
     </row>

--- a/ديمو/templates/05_العقد_والمقايسة.xlsx
+++ b/ديمو/templates/05_العقد_والمقايسة.xlsx
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>الإعمال المدنيــة</t>
+          <t>مثال — الإعمال المدنيــة</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>غرف التفتيش</t>
+          <t>مثال — غرف التفتيش</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>غرفة تفتيش طراز HH-I</t>
+          <t>مثال — غرفة تفتيش طراز HH-I</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>حفر ضيق Micro trenching عرض 10 إلى 13 سم</t>
+          <t>مثال — حفر ضيق Micro trenching عرض 10 إلى 13 سم</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>pulling of HDPE Single Microduct</t>
+          <t>مثال — pulling of HDPE Single Microduct</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"المقايسة": [["1", "الإعمال المدنيــة", "", "", "", ""], ["1-1", "غرف التفتيش", "", "", "", ""], ["1-1-1-2", "غرفة تفتيش طراز HH-I", "عدد", "180", "26000", "أعمال مدنية"], ["1-9-1", "حفر ضيق Micro trenching عرض 10 إلى 13 سم", "م.ط", "50000", "0", "أعمال مدنية"], ["2-4-7", "pulling of HDPE Single Microduct", "م.ط", "80000", "0", "تركيبات"]]}</t>
+          <t>{"المقايسة": [["1", "مثال — الإعمال المدنيــة", "", "", "", ""], ["1-1", "مثال — غرف التفتيش", "", "", "", ""], ["1-1-1-2", "مثال — غرفة تفتيش طراز HH-I", "عدد", "180", "26000", "أعمال مدنية"], ["1-9-1", "مثال — حفر ضيق Micro trenching عرض 10 إلى 13 سم", "م.ط", "50000", "0", "أعمال مدنية"], ["2-4-7", "مثال — pulling of HDPE Single Microduct", "م.ط", "80000", "0", "تركيبات"]]}</t>
         </is>
       </c>
     </row>
